--- a/data/plantilla_entitystatus.xlsx
+++ b/data/plantilla_entitystatus.xlsx
@@ -1,34 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\diego_enriquez_idico\idico_projects\actualizacion_insidesales\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB80DF0F-F779-4C17-AFE8-339FF0907268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="datos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>id_transaccion</t>
+  </si>
+  <si>
+    <t>id_entitystatus</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +62,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,28 +364,2116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B263"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="25.86" customWidth="1" min="1" max="1"/>
-    <col width="22.57" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="25.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id_transaccion</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id_entitystatus</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1248672</v>
+      </c>
+      <c r="B2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1268395</v>
+      </c>
+      <c r="B3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1285316</v>
+      </c>
+      <c r="B4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1282762</v>
+      </c>
+      <c r="B5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1282967</v>
+      </c>
+      <c r="B6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1285315</v>
+      </c>
+      <c r="B7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1288592</v>
+      </c>
+      <c r="B8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1308986</v>
+      </c>
+      <c r="B9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1308293</v>
+      </c>
+      <c r="B10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1306031</v>
+      </c>
+      <c r="B11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1309399</v>
+      </c>
+      <c r="B12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1314097</v>
+      </c>
+      <c r="B13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1312067</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1320104</v>
+      </c>
+      <c r="B15">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1322024</v>
+      </c>
+      <c r="B16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1327739</v>
+      </c>
+      <c r="B17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1338379</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1342976</v>
+      </c>
+      <c r="B19">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1361989</v>
+      </c>
+      <c r="B20">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1370069</v>
+      </c>
+      <c r="B21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1376516</v>
+      </c>
+      <c r="B22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1392454</v>
+      </c>
+      <c r="B23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1398285</v>
+      </c>
+      <c r="B24">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1405499</v>
+      </c>
+      <c r="B25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1419894</v>
+      </c>
+      <c r="B26">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1420414</v>
+      </c>
+      <c r="B27">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1418738</v>
+      </c>
+      <c r="B28">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1435283</v>
+      </c>
+      <c r="B29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1446967</v>
+      </c>
+      <c r="B30">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1448093</v>
+      </c>
+      <c r="B31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1458254</v>
+      </c>
+      <c r="B32">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1463344</v>
+      </c>
+      <c r="B33">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1480236</v>
+      </c>
+      <c r="B34">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1096226</v>
+      </c>
+      <c r="B35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1103155</v>
+      </c>
+      <c r="B36">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1134591</v>
+      </c>
+      <c r="B37">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1176089</v>
+      </c>
+      <c r="B38">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1276520</v>
+      </c>
+      <c r="B39">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1278247</v>
+      </c>
+      <c r="B40">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1282151</v>
+      </c>
+      <c r="B41">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1293565</v>
+      </c>
+      <c r="B42">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1291637</v>
+      </c>
+      <c r="B43">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1295926</v>
+      </c>
+      <c r="B44">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1308079</v>
+      </c>
+      <c r="B45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1312065</v>
+      </c>
+      <c r="B46">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1318886</v>
+      </c>
+      <c r="B47">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1320003</v>
+      </c>
+      <c r="B48">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1345933</v>
+      </c>
+      <c r="B49">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1350041</v>
+      </c>
+      <c r="B50">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1351997</v>
+      </c>
+      <c r="B51">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1353344</v>
+      </c>
+      <c r="B52">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1352410</v>
+      </c>
+      <c r="B53">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1354725</v>
+      </c>
+      <c r="B54">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1358959</v>
+      </c>
+      <c r="B55">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>1363326</v>
+      </c>
+      <c r="B56">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1367262</v>
+      </c>
+      <c r="B57">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1370501</v>
+      </c>
+      <c r="B58">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1374074</v>
+      </c>
+      <c r="B59">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1385541</v>
+      </c>
+      <c r="B60">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1460245</v>
+      </c>
+      <c r="B61">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1471838</v>
+      </c>
+      <c r="B62">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1478489</v>
+      </c>
+      <c r="B63">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1092950</v>
+      </c>
+      <c r="B64">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1144748</v>
+      </c>
+      <c r="B65">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1175991</v>
+      </c>
+      <c r="B66">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1219198</v>
+      </c>
+      <c r="B67">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1246702</v>
+      </c>
+      <c r="B68">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1274892</v>
+      </c>
+      <c r="B69">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1277134</v>
+      </c>
+      <c r="B70">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1288384</v>
+      </c>
+      <c r="B71">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1289508</v>
+      </c>
+      <c r="B72">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1298733</v>
+      </c>
+      <c r="B73">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1304406</v>
+      </c>
+      <c r="B74">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1314709</v>
+      </c>
+      <c r="B75">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1313487</v>
+      </c>
+      <c r="B76">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1319087</v>
+      </c>
+      <c r="B77">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1336451</v>
+      </c>
+      <c r="B78">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1344799</v>
+      </c>
+      <c r="B79">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1349743</v>
+      </c>
+      <c r="B80">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>1360634</v>
+      </c>
+      <c r="B81">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>1364092</v>
+      </c>
+      <c r="B82">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>1367257</v>
+      </c>
+      <c r="B83">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>1365800</v>
+      </c>
+      <c r="B84">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>1370182</v>
+      </c>
+      <c r="B85">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>1378621</v>
+      </c>
+      <c r="B86">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1398184</v>
+      </c>
+      <c r="B87">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>1396237</v>
+      </c>
+      <c r="B88">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1399647</v>
+      </c>
+      <c r="B89">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>1399446</v>
+      </c>
+      <c r="B90">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>1401823</v>
+      </c>
+      <c r="B91">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>1403663</v>
+      </c>
+      <c r="B92">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>1410243</v>
+      </c>
+      <c r="B93">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>1387228</v>
+      </c>
+      <c r="B94">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>1099892</v>
+      </c>
+      <c r="B95">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>1293261</v>
+      </c>
+      <c r="B96">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>1287968</v>
+      </c>
+      <c r="B97">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>1308284</v>
+      </c>
+      <c r="B98">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>1308488</v>
+      </c>
+      <c r="B99">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>1306546</v>
+      </c>
+      <c r="B100">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1312373</v>
+      </c>
+      <c r="B101">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1317542</v>
+      </c>
+      <c r="B102">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>1320103</v>
+      </c>
+      <c r="B103">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>1322734</v>
+      </c>
+      <c r="B104">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>1326522</v>
+      </c>
+      <c r="B105">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>1329274</v>
+      </c>
+      <c r="B106">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>1331446</v>
+      </c>
+      <c r="B107">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>1340621</v>
+      </c>
+      <c r="B108">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>1336452</v>
+      </c>
+      <c r="B109">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>1356249</v>
+      </c>
+      <c r="B110">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>1358125</v>
+      </c>
+      <c r="B111">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>1362293</v>
+      </c>
+      <c r="B112">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>1361560</v>
+      </c>
+      <c r="B113">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>1363777</v>
+      </c>
+      <c r="B114">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>1364507</v>
+      </c>
+      <c r="B115">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>1364088</v>
+      </c>
+      <c r="B116">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>1373260</v>
+      </c>
+      <c r="B117">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>1385642</v>
+      </c>
+      <c r="B118">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>1394609</v>
+      </c>
+      <c r="B119">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>1403563</v>
+      </c>
+      <c r="B120">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>1419387</v>
+      </c>
+      <c r="B121">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>1440607</v>
+      </c>
+      <c r="B122">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>1347492</v>
+      </c>
+      <c r="B123">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>1113821</v>
+      </c>
+      <c r="B124">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>1139563</v>
+      </c>
+      <c r="B125">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>1174861</v>
+      </c>
+      <c r="B126">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>1279913</v>
+      </c>
+      <c r="B127">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>1288792</v>
+      </c>
+      <c r="B128">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>1305727</v>
+      </c>
+      <c r="B129">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>1306648</v>
+      </c>
+      <c r="B130">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>1307976</v>
+      </c>
+      <c r="B131">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>1308492</v>
+      </c>
+      <c r="B132">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>1304613</v>
+      </c>
+      <c r="B133">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>1316839</v>
+      </c>
+      <c r="B134">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>1314605</v>
+      </c>
+      <c r="B135">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>1315013</v>
+      </c>
+      <c r="B136">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>1319394</v>
+      </c>
+      <c r="B137">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>1319802</v>
+      </c>
+      <c r="B138">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>1329376</v>
+      </c>
+      <c r="B139">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>1326523</v>
+      </c>
+      <c r="B140">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>1325401</v>
+      </c>
+      <c r="B141">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>1328457</v>
+      </c>
+      <c r="B142">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>1329475</v>
+      </c>
+      <c r="B143">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>1344694</v>
+      </c>
+      <c r="B144">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>1345823</v>
+      </c>
+      <c r="B145">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>1351372</v>
+      </c>
+      <c r="B146">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>1357599</v>
+      </c>
+      <c r="B147">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>1362186</v>
+      </c>
+      <c r="B148">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>1364732</v>
+      </c>
+      <c r="B149">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>1365697</v>
+      </c>
+      <c r="B150">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>1375015</v>
+      </c>
+      <c r="B151">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>1378723</v>
+      </c>
+      <c r="B152">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>1383285</v>
+      </c>
+      <c r="B153">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>1383184</v>
+      </c>
+      <c r="B154">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>1382671</v>
+      </c>
+      <c r="B155">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>1385232</v>
+      </c>
+      <c r="B156">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>1391428</v>
+      </c>
+      <c r="B157">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>1392456</v>
+      </c>
+      <c r="B158">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>1412904</v>
+      </c>
+      <c r="B159">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>1236763</v>
+      </c>
+      <c r="B160">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>1419074</v>
+      </c>
+      <c r="B161">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>1467937</v>
+      </c>
+      <c r="B162">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>1249396</v>
+      </c>
+      <c r="B163">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>1282152</v>
+      </c>
+      <c r="B164">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>1285014</v>
+      </c>
+      <c r="B165">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>1289200</v>
+      </c>
+      <c r="B166">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>1294601</v>
+      </c>
+      <c r="B167">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>1307665</v>
+      </c>
+      <c r="B168">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>1309394</v>
+      </c>
+      <c r="B169">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>1313990</v>
+      </c>
+      <c r="B170">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>1319594</v>
+      </c>
+      <c r="B171">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>1318183</v>
+      </c>
+      <c r="B172">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>1321723</v>
+      </c>
+      <c r="B173">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>1325294</v>
+      </c>
+      <c r="B174">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>1339403</v>
+      </c>
+      <c r="B175">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>1336765</v>
+      </c>
+      <c r="B176">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>1354978</v>
+      </c>
+      <c r="B177">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>1355095</v>
+      </c>
+      <c r="B178">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>1359397</v>
+      </c>
+      <c r="B179">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>1359808</v>
+      </c>
+      <c r="B180">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>1360635</v>
+      </c>
+      <c r="B181">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>1361771</v>
+      </c>
+      <c r="B182">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>1365072</v>
+      </c>
+      <c r="B183">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>1367637</v>
+      </c>
+      <c r="B184">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>1366948</v>
+      </c>
+      <c r="B185">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>1369665</v>
+      </c>
+      <c r="B186">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>1369468</v>
+      </c>
+      <c r="B187">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>1374801</v>
+      </c>
+      <c r="B188">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>1381009</v>
+      </c>
+      <c r="B189">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>1391947</v>
+      </c>
+      <c r="B190">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>1396862</v>
+      </c>
+      <c r="B191">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>1411369</v>
+      </c>
+      <c r="B192">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>1426663</v>
+      </c>
+      <c r="B193">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>1422067</v>
+      </c>
+      <c r="B194">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>1110747</v>
+      </c>
+      <c r="B195">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>1155572</v>
+      </c>
+      <c r="B196">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>1268918</v>
+      </c>
+      <c r="B197">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>1283269</v>
+      </c>
+      <c r="B198">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>1285824</v>
+      </c>
+      <c r="B199">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>1306134</v>
+      </c>
+      <c r="B200">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>1315218</v>
+      </c>
+      <c r="B201">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>1313188</v>
+      </c>
+      <c r="B202">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>1339399</v>
+      </c>
+      <c r="B203">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>1352312</v>
+      </c>
+      <c r="B204">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>1361561</v>
+      </c>
+      <c r="B205">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>1361248</v>
+      </c>
+      <c r="B206">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>1367374</v>
+      </c>
+      <c r="B207">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>1367155</v>
+      </c>
+      <c r="B208">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>1370282</v>
+      </c>
+      <c r="B209">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>1375646</v>
+      </c>
+      <c r="B210">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>1374382</v>
+      </c>
+      <c r="B211">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>1378619</v>
+      </c>
+      <c r="B212">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>1376621</v>
+      </c>
+      <c r="B213">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>1380805</v>
+      </c>
+      <c r="B214">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>1382363</v>
+      </c>
+      <c r="B215">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>1383495</v>
+      </c>
+      <c r="B216">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>1384417</v>
+      </c>
+      <c r="B217">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>1391534</v>
+      </c>
+      <c r="B218">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>1422979</v>
+      </c>
+      <c r="B219">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>1435707</v>
+      </c>
+      <c r="B220">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>1440706</v>
+      </c>
+      <c r="B221">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>1464780</v>
+      </c>
+      <c r="B222">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>1480028</v>
+      </c>
+      <c r="B223">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>1117916</v>
+      </c>
+      <c r="B224">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>1206028</v>
+      </c>
+      <c r="B225">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>1273075</v>
+      </c>
+      <c r="B226">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>1282761</v>
+      </c>
+      <c r="B227">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>1291639</v>
+      </c>
+      <c r="B228">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>1295829</v>
+      </c>
+      <c r="B229">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>1306338</v>
+      </c>
+      <c r="B230">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>1314298</v>
+      </c>
+      <c r="B231">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>1314810</v>
+      </c>
+      <c r="B232">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>1322127</v>
+      </c>
+      <c r="B233">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>1321925</v>
+      </c>
+      <c r="B234">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>1322427</v>
+      </c>
+      <c r="B235">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>1327128</v>
+      </c>
+      <c r="B236">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>1334293</v>
+      </c>
+      <c r="B237">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>1350458</v>
+      </c>
+      <c r="B238">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>1353244</v>
+      </c>
+      <c r="B239">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>1358333</v>
+      </c>
+      <c r="B240">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>1360943</v>
+      </c>
+      <c r="B241">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>1362188</v>
+      </c>
+      <c r="B242">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>1360939</v>
+      </c>
+      <c r="B243">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>1364627</v>
+      </c>
+      <c r="B244">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>1367485</v>
+      </c>
+      <c r="B245">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>1369473</v>
+      </c>
+      <c r="B246">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>1369966</v>
+      </c>
+      <c r="B247">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>1374802</v>
+      </c>
+      <c r="B248">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>1373262</v>
+      </c>
+      <c r="B249">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>1378408</v>
+      </c>
+      <c r="B250">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>1377554</v>
+      </c>
+      <c r="B251">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>1377560</v>
+      </c>
+      <c r="B252">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>1381014</v>
+      </c>
+      <c r="B253">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>1382873</v>
+      </c>
+      <c r="B254">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>1382361</v>
+      </c>
+      <c r="B255">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>1386826</v>
+      </c>
+      <c r="B256">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>1389285</v>
+      </c>
+      <c r="B257">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>1392353</v>
+      </c>
+      <c r="B258">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>1348811</v>
+      </c>
+      <c r="B259">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>1425339</v>
+      </c>
+      <c r="B260">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>1433116</v>
+      </c>
+      <c r="B261">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>1463345</v>
+      </c>
+      <c r="B262">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>1464680</v>
+      </c>
+      <c r="B263">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
